--- a/output/pdf_financials_xlsx/FRI.xlsx
+++ b/output/pdf_financials_xlsx/FRI.xlsx
@@ -6290,55 +6290,55 @@
         <v>0.28757</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.299955</v>
+        <v>0.308124</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.367095</v>
+        <v>0.389755</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.398458</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.784753</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.061528</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.061528</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.240228</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.313228</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>4.141028</v>
       </c>
     </row>
     <row r="93">
@@ -7940,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.556034</v>
+        <v>5e-06</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.095443</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
@@ -10038,7 +10038,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -11836,7 +11840,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12658,7 +12666,11 @@
           <t>Share-based payment reserve 5</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13192,7 +13204,11 @@
           <t>Share-based payment reserve 5</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -14462,7 +14478,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15764,7 +15784,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16168,7 +16192,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16688,7 +16716,11 @@
           <t>Share based payment reserve 8</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -22196,7 +22228,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -22990,7 +23026,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FRI.xlsx
+++ b/output/pdf_financials_xlsx/FRI.xlsx
@@ -1161,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.059793</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.045503</v>
       </c>
     </row>
     <row r="13">
@@ -2220,10 +2220,10 @@
         <v>-2.287501</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.233957</v>
+        <v>-4.29375</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-3.652343</v>
+        <v>-3.697846</v>
       </c>
     </row>
     <row r="28">
@@ -2350,10 +2350,10 @@
         <v>-2.287501</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.233957</v>
+        <v>-4.29375</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-3.652343</v>
+        <v>-3.697846</v>
       </c>
     </row>
     <row r="30">
@@ -2629,49 +2629,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.047577</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.076086</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.019847</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.439434</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001099</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.05232</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.020054</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00169</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000195</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000101</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001676</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.169379</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.435246</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.133567</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.633464</v>
@@ -2751,49 +2751,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.001009</v>
+        <v>0.048586</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.001009</v>
+        <v>0.077095</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.001009</v>
+        <v>0.020856</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.439434</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001099</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.05232</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.020054</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00169</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.0003</v>
+        <v>0.000495</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0003</v>
+        <v>0.000401</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001676</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.169379</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.435246</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.133567</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.633464</v>
@@ -3483,46 +3483,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.061877</v>
+        <v>0.0143</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.076086</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.019847</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.439734</v>
+        <v>0.0003</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.151399</v>
+        <v>0.1503</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.05262</v>
+        <v>0.0003</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.020354</v>
+        <v>0.0003</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00199</v>
+        <v>0.0003</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.000367</v>
+        <v>0.0003</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.000195</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.000971</v>
+        <v>0.00087</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.001676</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.302163</v>
+        <v>0.132784</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.564754</v>
+        <v>0.129508</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
